--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16444</v>
+        <v>16.98315</v>
       </c>
       <c r="D2" t="n">
-        <v>16.35939</v>
+        <v>16.59289</v>
       </c>
       <c r="E2" t="n">
-        <v>16.95975</v>
+        <v>16.75209</v>
       </c>
       <c r="F2" t="n">
-        <v>42.80187</v>
+        <v>42.72383</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05104</v>
+        <v>0.04995</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80192</v>
+        <v>1.85812</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.74277</v>
+        <v>16.83758</v>
       </c>
       <c r="D3" t="n">
-        <v>16.82641</v>
+        <v>16.47642</v>
       </c>
       <c r="E3" t="n">
-        <v>16.87999</v>
+        <v>16.53651</v>
       </c>
       <c r="F3" t="n">
-        <v>42.92989</v>
+        <v>42.13454</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05092</v>
+        <v>0.0504</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8055</v>
+        <v>1.82474</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65762</v>
+        <v>16.92703</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56487</v>
+        <v>16.46949</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75703</v>
+        <v>16.69263</v>
       </c>
       <c r="F4" t="n">
-        <v>42.60559</v>
+        <v>42.72299</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0503</v>
+        <v>0.05053</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83792</v>
+        <v>1.81106</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.9014</v>
+        <v>16.85455</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06083</v>
+        <v>15.90623</v>
       </c>
       <c r="E6" t="n">
-        <v>16.16976</v>
+        <v>16.3636</v>
       </c>
       <c r="F6" t="n">
-        <v>21.56446</v>
+        <v>21.60536</v>
       </c>
       <c r="G6" t="n">
-        <v>34.36548</v>
+        <v>33.83633</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.55792</v>
+        <v>16.62833</v>
       </c>
       <c r="D7" t="n">
-        <v>15.92401</v>
+        <v>16.14722</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61853</v>
+        <v>16.27033</v>
       </c>
       <c r="F7" t="n">
-        <v>21.54219</v>
+        <v>21.86465</v>
       </c>
       <c r="G7" t="n">
-        <v>34.55617</v>
+        <v>33.61034</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69363</v>
+        <v>16.68547</v>
       </c>
       <c r="D8" t="n">
-        <v>15.96189</v>
+        <v>15.79356</v>
       </c>
       <c r="E8" t="n">
-        <v>16.28683</v>
+        <v>16.33863</v>
       </c>
       <c r="F8" t="n">
-        <v>21.31764</v>
+        <v>21.53501</v>
       </c>
       <c r="G8" t="n">
-        <v>33.9605</v>
+        <v>33.90572</v>
       </c>
     </row>
   </sheetData>
